--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -45,11 +45,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="[$-42C]d\ mmm\ yy;@"/>
-    <numFmt numFmtId="165" formatCode="0\ &quot;gün&quot;"/>
-    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -428,7 +425,7 @@
         <v>projectTitle</v>
       </c>
       <c r="B2" t="str">
-        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI</v>
+        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI demo</v>
       </c>
     </row>
     <row r="3">

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -45,8 +45,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="[$-42C]d\ mmm\ yy;@"/>
+    <numFmt numFmtId="165" formatCode="0\ &quot;gün&quot;"/>
+    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -425,7 +428,7 @@
         <v>projectTitle</v>
       </c>
       <c r="B2" t="str">
-        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI demo</v>
+        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI</v>
       </c>
     </row>
     <row r="3">
@@ -838,7 +841,7 @@
         <v>packagesTrendNote</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Fərdi evlər üzrə faktiki icra (%) — hesabat vərəqlərinin tarixləri üzrə.</v>
       </c>
     </row>
     <row r="3">
@@ -869,18 +872,24 @@
       <c r="A6" t="str">
         <v>infraOverallPlan</v>
       </c>
+      <c r="B6">
+        <v>21.74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>infraOverallFakt</v>
       </c>
+      <c r="B7">
+        <v>20.78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>infraWeeklyNote</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Sahədaxili kommunikasiya işləri üzrə icra Primavera qrafikindən paketlərin orta göstəricisi kimi hesablanmışdır.</v>
       </c>
     </row>
     <row r="9">
@@ -1280,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1293,16 +1302,49 @@
         <v>plan</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>28.05.2026</v>
+      </c>
+      <c r="B2">
+        <v>43.62</v>
+      </c>
+      <c r="C2">
+        <v>52.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>04.06.2026</v>
+      </c>
+      <c r="B3">
+        <v>46.32</v>
+      </c>
+      <c r="C3">
+        <v>53.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>11.06.2026</v>
+      </c>
+      <c r="B4">
+        <v>49.64</v>
+      </c>
+      <c r="C4">
+        <v>56.06</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1324,9 +1366,369 @@
         <v>fakt</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C2">
+        <v>146</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>98.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C3">
+        <v>146</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E3">
+        <v>93.63</v>
+      </c>
+      <c r="F3">
+        <v>48.17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C4">
+        <v>146</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E4">
+        <v>31.14</v>
+      </c>
+      <c r="F4">
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C5">
+        <v>146</v>
+      </c>
+      <c r="D5" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E5">
+        <v>48.63</v>
+      </c>
+      <c r="F5">
+        <v>31.97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C6">
+        <v>146</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E6">
+        <v>34.82</v>
+      </c>
+      <c r="F6">
+        <v>38.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C7">
+        <v>146</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E7">
+        <v>6.21</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>97.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E9">
+        <v>93.63</v>
+      </c>
+      <c r="F9">
+        <v>59.54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E10">
+        <v>31.14</v>
+      </c>
+      <c r="F10">
+        <v>23.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+      <c r="D11" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E11">
+        <v>48.63</v>
+      </c>
+      <c r="F11">
+        <v>31.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E12">
+        <v>34.82</v>
+      </c>
+      <c r="F12">
+        <v>38.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E13">
+        <v>6.21</v>
+      </c>
+      <c r="F13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C14">
+        <v>86</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C15">
+        <v>86</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E15">
+        <v>93.63</v>
+      </c>
+      <c r="F15">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C16">
+        <v>86</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E16">
+        <v>31.14</v>
+      </c>
+      <c r="F16">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C17">
+        <v>86</v>
+      </c>
+      <c r="D17" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E17">
+        <v>48.63</v>
+      </c>
+      <c r="F17">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C18">
+        <v>86</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E18">
+        <v>34.82</v>
+      </c>
+      <c r="F18">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C19">
+        <v>86</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E19">
+        <v>6.21</v>
+      </c>
+      <c r="F19">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1400,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1413,9 +1815,64 @@
         <v>fakt</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Elektrik / zəif cərəyan</v>
+      </c>
+      <c r="B2">
+        <v>73.98</v>
+      </c>
+      <c r="C2">
+        <v>36.21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Su və kanalizasiya</v>
+      </c>
+      <c r="B3">
+        <v>5.56</v>
+      </c>
+      <c r="C3">
+        <v>33.34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Qaz təchizatı</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>İstilik və ventilyasiya</v>
+      </c>
+      <c r="B5">
+        <v>29.17</v>
+      </c>
+      <c r="C5">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Rabitə şəbəkəsi</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -1344,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1377,13 +1377,13 @@
         <v>146</v>
       </c>
       <c r="D2" t="str">
-        <v>Qaba işlər</v>
+        <v>Hörgü işləri</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
       <c r="F2">
-        <v>98.16</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="3">
@@ -1488,22 +1488,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>p1</v>
+        <v>cemi</v>
       </c>
       <c r="B8" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Cəmi (146 ev)</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="D8" t="str">
-        <v>Qaba işlər</v>
+        <v>Qapı və pəncərə</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>31.03</v>
       </c>
       <c r="F8">
-        <v>97.33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1517,13 +1517,13 @@
         <v>60</v>
       </c>
       <c r="D9" t="str">
-        <v>Dam örtüyü</v>
+        <v>Qaba işlər</v>
       </c>
       <c r="E9">
-        <v>93.63</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>59.54</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="10">
@@ -1537,13 +1537,13 @@
         <v>60</v>
       </c>
       <c r="D10" t="str">
-        <v>Daxili bəzək</v>
+        <v>Dam örtüyü</v>
       </c>
       <c r="E10">
-        <v>31.14</v>
+        <v>93.63</v>
       </c>
       <c r="F10">
-        <v>23.83</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="11">
@@ -1557,13 +1557,13 @@
         <v>60</v>
       </c>
       <c r="D11" t="str">
-        <v>MEP</v>
+        <v>Daxili bəzək</v>
       </c>
       <c r="E11">
-        <v>48.63</v>
+        <v>31.14</v>
       </c>
       <c r="F11">
-        <v>31.14</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="12">
@@ -1577,13 +1577,13 @@
         <v>60</v>
       </c>
       <c r="D12" t="str">
-        <v>Xarici bəzək (fasad)</v>
+        <v>MEP</v>
       </c>
       <c r="E12">
-        <v>34.82</v>
+        <v>48.63</v>
       </c>
       <c r="F12">
-        <v>38.36</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="13">
@@ -1597,33 +1597,33 @@
         <v>60</v>
       </c>
       <c r="D13" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>Xarici bəzək (fasad)</v>
       </c>
       <c r="E13">
-        <v>6.21</v>
+        <v>34.82</v>
       </c>
       <c r="F13">
-        <v>4.8</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>p2</v>
+        <v>p1</v>
       </c>
       <c r="B14" t="str">
-        <v>Sahə 3 (86 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C14">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D14" t="str">
-        <v>Qaba işlər</v>
+        <v>Təsərrüfat / tamamlama</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>6.21</v>
       </c>
       <c r="F14">
-        <v>99</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="15">
@@ -1637,13 +1637,13 @@
         <v>86</v>
       </c>
       <c r="D15" t="str">
-        <v>Dam örtüyü</v>
+        <v>Qaba işlər</v>
       </c>
       <c r="E15">
-        <v>93.63</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>36.8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>86</v>
       </c>
       <c r="D16" t="str">
-        <v>Daxili bəzək</v>
+        <v>Dam örtüyü</v>
       </c>
       <c r="E16">
-        <v>31.14</v>
+        <v>93.63</v>
       </c>
       <c r="F16">
-        <v>20.71</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="17">
@@ -1677,13 +1677,13 @@
         <v>86</v>
       </c>
       <c r="D17" t="str">
-        <v>MEP</v>
+        <v>Daxili bəzək</v>
       </c>
       <c r="E17">
-        <v>48.63</v>
+        <v>31.14</v>
       </c>
       <c r="F17">
-        <v>32.79</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="18">
@@ -1697,13 +1697,13 @@
         <v>86</v>
       </c>
       <c r="D18" t="str">
-        <v>Xarici bəzək (fasad)</v>
+        <v>MEP</v>
       </c>
       <c r="E18">
-        <v>34.82</v>
+        <v>48.63</v>
       </c>
       <c r="F18">
-        <v>38.46</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="19">
@@ -1717,18 +1717,38 @@
         <v>86</v>
       </c>
       <c r="D19" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E19">
+        <v>34.82</v>
+      </c>
+      <c r="F19">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Sahə 3 (86 ev)</v>
+      </c>
+      <c r="C20">
+        <v>86</v>
+      </c>
+      <c r="D20" t="str">
         <v>Təsərrüfat / tamamlama</v>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>6.21</v>
       </c>
-      <c r="F19">
+      <c r="F20">
         <v>3.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F20"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -1344,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1368,13 +1368,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B2" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C2">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D2" t="str">
         <v>Hörgü işləri</v>
@@ -1388,13 +1388,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B3" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C3">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D3" t="str">
         <v>Dam örtüyü</v>
@@ -1403,18 +1403,18 @@
         <v>93.63</v>
       </c>
       <c r="F3">
-        <v>48.17</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B4" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C4">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D4" t="str">
         <v>Daxili bəzək</v>
@@ -1423,18 +1423,18 @@
         <v>31.14</v>
       </c>
       <c r="F4">
-        <v>22.27</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B5" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C5">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D5" t="str">
         <v>MEP</v>
@@ -1443,18 +1443,18 @@
         <v>48.63</v>
       </c>
       <c r="F5">
-        <v>31.97</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B6" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C6">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D6" t="str">
         <v>Xarici bəzək (fasad)</v>
@@ -1463,38 +1463,38 @@
         <v>34.82</v>
       </c>
       <c r="F6">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B7" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C7">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D7" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>Mebel</v>
       </c>
       <c r="E7">
-        <v>6.21</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B8" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C8">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D8" t="str">
         <v>Qapı və pəncərə</v>
@@ -1517,113 +1517,113 @@
         <v>60</v>
       </c>
       <c r="D9" t="str">
-        <v>Qaba işlər</v>
+        <v xml:space="preserve">Həyətyanı işlər </v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>97.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B10" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D10" t="str">
-        <v>Dam örtüyü</v>
+        <v>Qaba işlər</v>
       </c>
       <c r="E10">
-        <v>93.63</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>59.54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B11" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D11" t="str">
-        <v>Daxili bəzək</v>
+        <v>Dam örtüyü</v>
       </c>
       <c r="E11">
-        <v>31.14</v>
+        <v>93.63</v>
       </c>
       <c r="F11">
-        <v>23.83</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B12" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D12" t="str">
-        <v>MEP</v>
+        <v>Daxili bəzək</v>
       </c>
       <c r="E12">
-        <v>48.63</v>
+        <v>31.14</v>
       </c>
       <c r="F12">
-        <v>31.14</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B13" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C13">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D13" t="str">
-        <v>Xarici bəzək (fasad)</v>
+        <v>MEP</v>
       </c>
       <c r="E13">
-        <v>34.82</v>
+        <v>48.63</v>
       </c>
       <c r="F13">
-        <v>38.36</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B14" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D14" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>Xarici bəzək (fasad)</v>
       </c>
       <c r="E14">
-        <v>6.21</v>
+        <v>34.82</v>
       </c>
       <c r="F14">
-        <v>4.8</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="15">
@@ -1631,124 +1631,24 @@
         <v>p2</v>
       </c>
       <c r="B15" t="str">
-        <v>Sahə 3 (86 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C15">
         <v>86</v>
       </c>
       <c r="D15" t="str">
-        <v>Qaba işlər</v>
+        <v>Təsərrüfat / tamamlama</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>6.21</v>
       </c>
       <c r="F15">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Sahə 3 (86 ev)</v>
-      </c>
-      <c r="C16">
-        <v>86</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Dam örtüyü</v>
-      </c>
-      <c r="E16">
-        <v>93.63</v>
-      </c>
-      <c r="F16">
-        <v>36.8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Sahə 3 (86 ev)</v>
-      </c>
-      <c r="C17">
-        <v>86</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Daxili bəzək</v>
-      </c>
-      <c r="E17">
-        <v>31.14</v>
-      </c>
-      <c r="F17">
-        <v>20.71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Sahə 3 (86 ev)</v>
-      </c>
-      <c r="C18">
-        <v>86</v>
-      </c>
-      <c r="D18" t="str">
-        <v>MEP</v>
-      </c>
-      <c r="E18">
-        <v>48.63</v>
-      </c>
-      <c r="F18">
-        <v>32.79</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Sahə 3 (86 ev)</v>
-      </c>
-      <c r="C19">
-        <v>86</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Xarici bəzək (fasad)</v>
-      </c>
-      <c r="E19">
-        <v>34.82</v>
-      </c>
-      <c r="F19">
-        <v>38.46</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Sahə 3 (86 ev)</v>
-      </c>
-      <c r="C20">
-        <v>86</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Təsərrüfat / tamamlama</v>
-      </c>
-      <c r="E20">
-        <v>6.21</v>
-      </c>
-      <c r="F20">
         <v>3.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -1344,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1477,13 +1477,13 @@
         <v>60</v>
       </c>
       <c r="D7" t="str">
-        <v>Mebel</v>
+        <v>Qapı və pəncərə</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31.03</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -1497,13 +1497,13 @@
         <v>60</v>
       </c>
       <c r="D8" t="str">
-        <v>Qapı və pəncərə</v>
+        <v>Mebel</v>
       </c>
       <c r="E8">
-        <v>31.03</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="D9" t="str">
-        <v xml:space="preserve">Həyətyanı işlər </v>
+        <v>Həyətyanı işlər</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1537,13 +1537,13 @@
         <v>86</v>
       </c>
       <c r="D10" t="str">
-        <v>Qaba işlər</v>
+        <v>Hörgü işləri</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -1637,18 +1637,58 @@
         <v>86</v>
       </c>
       <c r="D15" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>Qapı və pəncərə</v>
       </c>
       <c r="E15">
-        <v>6.21</v>
+        <v>31.03</v>
       </c>
       <c r="F15">
-        <v>3.6</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C16">
+        <v>86</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Mebel</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C17">
+        <v>86</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Həyətyanı işlər</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -425,7 +425,7 @@
         <v>projectTitle</v>
       </c>
       <c r="B2" t="str">
-        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI demo</v>
+        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI</v>
       </c>
     </row>
     <row r="3">
@@ -838,7 +838,7 @@
         <v>packagesTrendNote</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Fərdi evlər üzrə faktiki icra (%) — hesabat vərəqlərinin tarixləri üzrə.</v>
       </c>
     </row>
     <row r="3">
@@ -869,18 +869,24 @@
       <c r="A6" t="str">
         <v>infraOverallPlan</v>
       </c>
+      <c r="B6">
+        <v>21.74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>infraOverallFakt</v>
       </c>
+      <c r="B7">
+        <v>20.78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>infraWeeklyNote</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Sahədaxili kommunikasiya işləri hər paket üzrə ayrıca göstərilir (Primavera qrafikindən).</v>
       </c>
     </row>
     <row r="9">
@@ -1280,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1293,16 +1299,32 @@
         <v>plan</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>23.04.2026</v>
+      </c>
+      <c r="B2">
+        <v>35.87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>11.06.2026</v>
+      </c>
+      <c r="B3">
+        <v>52.57</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1324,9 +1346,369 @@
         <v>fakt</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C2">
+        <v>146</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>98.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C3">
+        <v>146</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E3">
+        <v>93.63</v>
+      </c>
+      <c r="F3">
+        <v>48.17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C4">
+        <v>146</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E4">
+        <v>31.14</v>
+      </c>
+      <c r="F4">
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C5">
+        <v>146</v>
+      </c>
+      <c r="D5" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E5">
+        <v>48.63</v>
+      </c>
+      <c r="F5">
+        <v>31.97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C6">
+        <v>146</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E6">
+        <v>34.82</v>
+      </c>
+      <c r="F6">
+        <v>38.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>cemi</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Cəmi (146 ev)</v>
+      </c>
+      <c r="C7">
+        <v>146</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E7">
+        <v>6.21</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>97.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E9">
+        <v>93.63</v>
+      </c>
+      <c r="F9">
+        <v>59.54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E10">
+        <v>31.14</v>
+      </c>
+      <c r="F10">
+        <v>23.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+      <c r="D11" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E11">
+        <v>48.63</v>
+      </c>
+      <c r="F11">
+        <v>31.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E12">
+        <v>34.82</v>
+      </c>
+      <c r="F12">
+        <v>38.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E13">
+        <v>6.21</v>
+      </c>
+      <c r="F13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C14">
+        <v>86</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Qaba işlər</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C15">
+        <v>86</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Dam örtüyü</v>
+      </c>
+      <c r="E15">
+        <v>93.63</v>
+      </c>
+      <c r="F15">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C16">
+        <v>86</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Daxili bəzək</v>
+      </c>
+      <c r="E16">
+        <v>31.14</v>
+      </c>
+      <c r="F16">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C17">
+        <v>86</v>
+      </c>
+      <c r="D17" t="str">
+        <v>MEP</v>
+      </c>
+      <c r="E17">
+        <v>48.63</v>
+      </c>
+      <c r="F17">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C18">
+        <v>86</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Xarici bəzək (fasad)</v>
+      </c>
+      <c r="E18">
+        <v>34.82</v>
+      </c>
+      <c r="F18">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>p2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C19">
+        <v>86</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Təsərrüfat / tamamlama</v>
+      </c>
+      <c r="E19">
+        <v>6.21</v>
+      </c>
+      <c r="F19">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1400,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1413,9 +1795,64 @@
         <v>fakt</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Elektrik / zəif axın</v>
+      </c>
+      <c r="B2">
+        <v>73.98</v>
+      </c>
+      <c r="C2">
+        <v>36.21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Su kanalizasiya</v>
+      </c>
+      <c r="B3">
+        <v>5.56</v>
+      </c>
+      <c r="C3">
+        <v>33.34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>İsitmə ventilyasiya</v>
+      </c>
+      <c r="B4">
+        <v>29.17</v>
+      </c>
+      <c r="C4">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Qaz təchizatı</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Kommunikasiya birləşmələri</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -45,11 +45,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="[$-42C]d\ mmm\ yy;@"/>
-    <numFmt numFmtId="165" formatCode="0\ &quot;gün&quot;"/>
-    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -428,7 +425,7 @@
         <v>projectTitle</v>
       </c>
       <c r="B2" t="str">
-        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI</v>
+        <v>Pirəhmədli kəndi üzrə tikinti gedişatı hesabatı</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +457,7 @@
         <v>reportDate</v>
       </c>
       <c r="B6" t="str">
-        <v>11.06.2026</v>
+        <v>18.06.2026</v>
       </c>
     </row>
     <row r="7">
@@ -889,7 +886,7 @@
         <v>infraWeeklyNote</v>
       </c>
       <c r="B8" t="str">
-        <v>Sahədaxili kommunikasiya işləri üzrə icra Primavera qrafikindən paketlərin orta göstəricisi kimi hesablanmışdır.</v>
+        <v>Sahədaxili kommunikasiya işləri hər paket üzrə ayrıca göstərilir (Primavera qrafikindən).</v>
       </c>
     </row>
     <row r="9">
@@ -1777,7 +1774,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Elektrik / zəif cərəyan</v>
+        <v>Elektrik / zəif axın</v>
       </c>
       <c r="B2">
         <v>73.98</v>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Su və kanalizasiya</v>
+        <v>Su kanalizasiya</v>
       </c>
       <c r="B3">
         <v>5.56</v>
@@ -1799,29 +1796,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Qaz təchizatı</v>
+        <v>İsitmə ventilyasiya</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>29.17</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>İstilik və ventilyasiya</v>
+        <v>Qaz təchizatı</v>
       </c>
       <c r="B5">
-        <v>29.17</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>34.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Rabitə şəbəkəsi</v>
+        <v>Kommunikasiya birləşmələri</v>
       </c>
       <c r="B6">
         <v>0</v>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -425,7 +425,7 @@
         <v>projectTitle</v>
       </c>
       <c r="B2" t="str">
-        <v>PIRƏHMƏDLI KƏNDI — TIKINTI GEDIŞATI HESABATI</v>
+        <v>Pirəhmədli kəndi üzrə tikinti gedişatı hesabatı</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         <v>reportDate</v>
       </c>
       <c r="B6" t="str">
-        <v>11.06.2026</v>
+        <v>18.06.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1286,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1301,30 +1301,47 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>23.04.2026</v>
+        <v>28.05.2026</v>
       </c>
       <c r="B2">
-        <v>35.87</v>
+        <v>43.62</v>
+      </c>
+      <c r="C2">
+        <v>52.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>04.06.2026</v>
+      </c>
+      <c r="B3">
+        <v>46.32</v>
+      </c>
+      <c r="C3">
+        <v>53.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
         <v>11.06.2026</v>
       </c>
-      <c r="B3">
-        <v>52.57</v>
+      <c r="B4">
+        <v>49.64</v>
+      </c>
+      <c r="C4">
+        <v>56.06</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1348,33 +1365,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B2" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C2">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D2" t="str">
-        <v>Qaba işlər</v>
+        <v>Hörgü işləri</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
       <c r="F2">
-        <v>98.16</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B3" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C3">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D3" t="str">
         <v>Dam örtüyü</v>
@@ -1383,18 +1400,18 @@
         <v>93.63</v>
       </c>
       <c r="F3">
-        <v>48.17</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B4" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C4">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D4" t="str">
         <v>Daxili bəzək</v>
@@ -1403,18 +1420,18 @@
         <v>31.14</v>
       </c>
       <c r="F4">
-        <v>22.27</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B5" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C5">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D5" t="str">
         <v>MEP</v>
@@ -1423,18 +1440,18 @@
         <v>48.63</v>
       </c>
       <c r="F5">
-        <v>31.97</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B6" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C6">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D6" t="str">
         <v>Xarici bəzək (fasad)</v>
@@ -1443,27 +1460,27 @@
         <v>34.82</v>
       </c>
       <c r="F6">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cemi</v>
+        <v>p1</v>
       </c>
       <c r="B7" t="str">
-        <v>Cəmi (146 ev)</v>
+        <v>Sahə 1 (60 ev)</v>
       </c>
       <c r="C7">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D7" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>Qapı və pəncərə</v>
       </c>
       <c r="E7">
-        <v>6.21</v>
+        <v>31.03</v>
       </c>
       <c r="F7">
-        <v>4.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -1477,13 +1494,13 @@
         <v>60</v>
       </c>
       <c r="D8" t="str">
-        <v>Qaba işlər</v>
+        <v>Mebel</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>97.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1497,93 +1514,93 @@
         <v>60</v>
       </c>
       <c r="D9" t="str">
-        <v>Dam örtüyü</v>
+        <v>Həyətyanı işlər</v>
       </c>
       <c r="E9">
-        <v>93.63</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>59.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B10" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D10" t="str">
-        <v>Daxili bəzək</v>
+        <v>Hörgü işləri</v>
       </c>
       <c r="E10">
-        <v>31.14</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>23.83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B11" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D11" t="str">
-        <v>MEP</v>
+        <v>Dam örtüyü</v>
       </c>
       <c r="E11">
-        <v>48.63</v>
+        <v>93.63</v>
       </c>
       <c r="F11">
-        <v>31.14</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B12" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D12" t="str">
-        <v>Xarici bəzək (fasad)</v>
+        <v>Daxili bəzək</v>
       </c>
       <c r="E12">
-        <v>34.82</v>
+        <v>31.14</v>
       </c>
       <c r="F12">
-        <v>38.36</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>p1</v>
+        <v>p2</v>
       </c>
       <c r="B13" t="str">
-        <v>Sahə 1 (60 ev)</v>
+        <v>Sahə 2 (86 ev)</v>
       </c>
       <c r="C13">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D13" t="str">
-        <v>Təsərrüfat / tamamlama</v>
+        <v>MEP</v>
       </c>
       <c r="E13">
-        <v>6.21</v>
+        <v>48.63</v>
       </c>
       <c r="F13">
-        <v>4.8</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="14">
@@ -1597,13 +1614,13 @@
         <v>86</v>
       </c>
       <c r="D14" t="str">
-        <v>Qaba işlər</v>
+        <v>Xarici bəzək (fasad)</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>34.82</v>
       </c>
       <c r="F14">
-        <v>99</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="15">
@@ -1617,13 +1634,13 @@
         <v>86</v>
       </c>
       <c r="D15" t="str">
-        <v>Dam örtüyü</v>
+        <v>Qapı və pəncərə</v>
       </c>
       <c r="E15">
-        <v>93.63</v>
+        <v>31.03</v>
       </c>
       <c r="F15">
-        <v>36.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1637,13 +1654,13 @@
         <v>86</v>
       </c>
       <c r="D16" t="str">
-        <v>Daxili bəzək</v>
+        <v>Mebel</v>
       </c>
       <c r="E16">
-        <v>31.14</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>20.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1657,58 +1674,18 @@
         <v>86</v>
       </c>
       <c r="D17" t="str">
-        <v>MEP</v>
+        <v>Həyətyanı işlər</v>
       </c>
       <c r="E17">
-        <v>48.63</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>32.79</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Sahə 2 (86 ev)</v>
-      </c>
-      <c r="C18">
-        <v>86</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Xarici bəzək (fasad)</v>
-      </c>
-      <c r="E18">
-        <v>34.82</v>
-      </c>
-      <c r="F18">
-        <v>38.46</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Sahə 2 (86 ev)</v>
-      </c>
-      <c r="C19">
-        <v>86</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Təsərrüfat / tamamlama</v>
-      </c>
-      <c r="E19">
-        <v>6.21</v>
-      </c>
-      <c r="F19">
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cities/pirehmedli-kendi/source.xlsx
+++ b/cities/pirehmedli-kendi/source.xlsx
@@ -823,7 +823,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -886,7 +886,7 @@
         <v>infraWeeklyNote</v>
       </c>
       <c r="B8" t="str">
-        <v>Sahədaxili kommunikasiya işləri hər paket üzrə ayrıca göstərilir (Primavera qrafikindən).</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -969,9 +969,33 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>hiddenSections</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>hiddenCharts</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ch-otherGap,ch-velCompliance</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>labelOverrides</v>
+      </c>
+      <c r="B21" t="str">
+        <v>{"sections":{},"charts":{},"footer":{}}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1759,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1772,71 +1796,16 @@
         <v>fakt</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Elektrik / zəif axın</v>
-      </c>
-      <c r="B2">
-        <v>73.98</v>
-      </c>
-      <c r="C2">
-        <v>36.21</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Su kanalizasiya</v>
-      </c>
-      <c r="B3">
-        <v>5.56</v>
-      </c>
-      <c r="C3">
-        <v>33.34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>İsitmə ventilyasiya</v>
-      </c>
-      <c r="B4">
-        <v>29.17</v>
-      </c>
-      <c r="C4">
-        <v>34.35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Qaz təchizatı</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Kommunikasiya birləşmələri</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1855,9 +1824,179 @@
         <v>fakt</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>inf1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Elektrik / zəif axın</v>
+      </c>
+      <c r="D2">
+        <v>73.98</v>
+      </c>
+      <c r="E2">
+        <v>41.38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>inf1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C3" t="str">
+        <v xml:space="preserve">Su kanalizasiyası </v>
+      </c>
+      <c r="D3">
+        <v>5.56</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>inf1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>İsitmə ventilyasiya</v>
+      </c>
+      <c r="D4">
+        <v>29.17</v>
+      </c>
+      <c r="E4">
+        <v>34.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>inf1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C5" t="str">
+        <v xml:space="preserve">Qaz təchizatı </v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>inf1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Sahə 1 (60 ev)</v>
+      </c>
+      <c r="C6" t="str">
+        <v xml:space="preserve">Kommunikasiya birləşmələri </v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>inf2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Elektrik / zəif axın</v>
+      </c>
+      <c r="D7">
+        <v>73.98</v>
+      </c>
+      <c r="E7">
+        <v>31.03</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>inf2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Su kanalizasiyası</v>
+      </c>
+      <c r="D8">
+        <v>5.56</v>
+      </c>
+      <c r="E8">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>inf2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>İsitmə ventilyasiya</v>
+      </c>
+      <c r="D9">
+        <v>29.17</v>
+      </c>
+      <c r="E9">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>inf2</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C10" t="str">
+        <v xml:space="preserve">Qaz təchizatı </v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>inf2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sahə 2 (86 ev)</v>
+      </c>
+      <c r="C11" t="str">
+        <v xml:space="preserve">Kommunikasiya birləşmələri </v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>